--- a/OriginalInitialSol_P50M2-0_prob_10.xlsx
+++ b/OriginalInitialSol_P50M2-0_prob_10.xlsx
@@ -447,46 +447,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5260000000163012</v>
+        <v>4720000000181780</v>
       </c>
       <c r="B2" t="n">
         <v>246042.18342432</v>
       </c>
       <c r="C2" t="n">
-        <v>7.370628356933594</v>
+        <v>6.054327487945557</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2140000000251491</v>
+        <v>1880000000260071</v>
       </c>
       <c r="B3" t="n">
         <v>246042.18342432</v>
       </c>
       <c r="C3" t="n">
-        <v>14.48390889167786</v>
+        <v>11.87521767616272</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>760000000289712.8</v>
+        <v>1180000000276793</v>
       </c>
       <c r="B4" t="n">
         <v>246042.18342432</v>
       </c>
       <c r="C4" t="n">
-        <v>21.84882926940918</v>
+        <v>17.85810279846191</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>900000000278949.9</v>
+        <v>1120000000278771</v>
       </c>
       <c r="B5" t="n">
-        <v>246042.18342432</v>
+        <v>245888.21827872</v>
       </c>
       <c r="C5" t="n">
-        <v>29.06649351119995</v>
+        <v>23.86089777946472</v>
       </c>
     </row>
   </sheetData>
